--- a/4 четверть_9_JavaScript_Vue.xlsx
+++ b/4 четверть_9_JavaScript_Vue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45559D31-AAFB-4191-8C89-562D186D0B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D4ED4-F60B-426D-BFC4-11E4C350C1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2790" yWindow="-17325" windowWidth="27330" windowHeight="12000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Название 1-3" sheetId="12" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="515">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -8017,17 +8017,611 @@
 &lt;/script&gt;</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    &lt;div class="gr-bd_content_receiveraddmenu" &gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        &lt;transition name="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>slide-fade</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;ReceiverAddMenu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v-if="mods.modAddReceiver"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+                :mailReceiversInGrp="mailReceiversInGrp"
+                :groupSelected="groupSelected"
+                @updateAllMailReceiversByGroupId="getAllMailReceiversByGroupId()"
+                @updateGroupsOfMlRcvs="updateGroupsOfMlRcvs()"
+                @exitReceiverAddMenu="Object.set(mods, 'modAddReceiver', false);"
+            </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;&lt;/ReceiverAddMenu&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        &lt;/transition&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    &lt;/div&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Когда нужно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Когда используется v-if, однако требуется анимация. Если использовать нативный подход, анимация не сработает. В связи с этим необходимо использовать встроенный компонент </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Пояснение! </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> должен выступать оберткой компонента, который необходимо анимировать.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v-if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> указывается на компоненте-потомке </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transition</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        &amp;_receiveraddmenu {
+            position: absolute;
+            top: 0px;
+            left: 0px;
+            width: 100%;
+            background-color: transparent;
+            z-index: 1;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">            &amp; .slide-fade-enter-active,
+            &amp; .slide-fade-leave-active {
+              transition: transform 0.7s ease;
+              will-change: transform; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/* Оптимизация для браузера */</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            }
+            &amp; .slide-fade-enter,
+            &amp; .slide-fade-leave-to {
+              transform: translateX(100%);</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //появление справа-налево</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+              transform: translateX(-100%); </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//появление слева-направо</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            }
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            &amp; .anchor {
+                position: relative;
+                z-index: 2;
+                &amp; .component-exit {
+                    position: absolute;
+                    left: 0px;
+                    top: 5px;
+                    width: 50px;
+                    height: 35px;
+                    background-color: #182649;
+                    border-radius: 20px;
+                    color: white;
+                    display: flex;
+                    align-items: center;
+                    padding-left: 7px;
+                    z-index: -1;
+                    cursor: pointer;
+                }
+                &amp; .ra-menu_container {
+                    width: calc(100% - 26px);
+                    height: 475px;
+                    background-color: white;
+                    -webkit-box-shadow: -35px 0px 40px -13px rgba(34, 60, 80, 0.27);
+                    -moz-box-shadow: -35px 0px 40px -13px rgba(34, 60, 80, 0.27);
+                    box-shadow: 0 5px 30px 0 rgba(0,0,0,0.2);
+                    margin: 30px 10px 20px 25px;
+                    padding: 10px 20px;
+                    z-index: 2;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Анимация</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Как должна работать анимация при первом вызове (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.slide-fade-enter-active</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) анимации и при втором вызове (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.slide-fade-leave-active</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&amp; .slide-fade-enter-active,
+&amp; .slide-fade-leave-active {
+ transition: transform 0.7s ease;
+ will-change: transform; 
+}
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Где должен располагаться элемент перед(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.slide-fade-enter</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)/после(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.slide-fade-leave-to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) анимации</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&amp; .slide-fade-enter,
+&amp; .slide-fade-leave-to {
+ transform: translateX(100%); //появление справа-налево
+ transform: translateX(-100%); //появление слева-направо
+}</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8449,11 +9043,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -8464,20 +9058,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -8489,7 +9083,7 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -8498,80 +9092,83 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="18" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="14" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="12" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="14" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -8580,28 +9177,43 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -8610,68 +9222,53 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{141A142D-D8A7-43F9-B8D2-54AA311FA1CB}"/>
     <cellStyle name="Обычный 2 2" xfId="3" xr:uid="{C739D4B1-2A16-47B8-8914-B47AE649C078}"/>
   </cellStyles>
@@ -9746,7 +10343,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V283"/>
+  <dimension ref="A2:V285"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -12051,13 +12648,13 @@
       </c>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="1:3" ht="28.8">
+    <row r="273" spans="1:4" ht="28.8">
       <c r="A273" s="2"/>
       <c r="C273" s="44" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="57.6">
+    <row r="274" spans="1:4" ht="57.6">
       <c r="A274" s="44" t="s">
         <v>439</v>
       </c>
@@ -12065,74 +12662,94 @@
         <v>440</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
-      <c r="A275" s="12" t="s">
+    <row r="275" spans="1:4">
+      <c r="A275" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="C275" s="44"/>
+    </row>
+    <row r="276" spans="1:4" ht="409.6">
+      <c r="A276" s="74" t="s">
+        <v>512</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C276" s="74" t="s">
+        <v>513</v>
+      </c>
+      <c r="D276" s="74" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="B277" s="41" t="s">
         <v>451</v>
       </c>
-      <c r="C275" s="44"/>
-    </row>
-    <row r="276" spans="1:3" ht="30">
-      <c r="A276" s="2" t="s">
+      <c r="C277" s="44"/>
+    </row>
+    <row r="278" spans="1:4" ht="30">
+      <c r="A278" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="B278" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="C276" s="45" t="s">
+      <c r="C278" s="45" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="60">
-      <c r="A277" s="2" t="s">
+    <row r="279" spans="1:4" ht="60">
+      <c r="A279" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C277" s="45" t="s">
+      <c r="C279" s="45" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="45">
-      <c r="A278" s="2" t="s">
+    <row r="280" spans="1:4" ht="45">
+      <c r="A280" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C278" s="45" t="s">
+      <c r="C280" s="45" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="28.8">
-      <c r="A279" s="2" t="s">
+    <row r="281" spans="1:4" ht="28.8">
+      <c r="A281" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="B281" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C279" s="44"/>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="2"/>
-      <c r="C280" s="44"/>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" s="2"/>
       <c r="C281" s="44"/>
     </row>
-    <row r="282" spans="1:3" ht="302.39999999999998">
-      <c r="B282" s="2" t="s">
+    <row r="282" spans="1:4">
+      <c r="A282" s="2"/>
+      <c r="C282" s="44"/>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="2"/>
+      <c r="C283" s="44"/>
+    </row>
+    <row r="284" spans="1:4" ht="302.39999999999998">
+      <c r="B284" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C282" s="46" t="s">
+      <c r="C284" s="46" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="216">
-      <c r="C283" s="46" t="s">
+    <row r="285" spans="1:4" ht="216">
+      <c r="C285" s="46" t="s">
         <v>441</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -12147,82 +12764,82 @@
   <dimension ref="A1:V14"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36" style="66" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="67" customWidth="1"/>
-    <col min="3" max="3" width="100.44140625" style="67" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="66" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="65" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="66" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="67" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="66" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="66" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="65" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="66" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="66" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="66" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="66" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="65" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="67" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="67" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="67" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="66" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="68"/>
-    <col min="21" max="21" width="67.77734375" style="67" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="66" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="66" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="66" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="66" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="66" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="66"/>
+    <col min="1" max="1" width="36" style="63" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="64" customWidth="1"/>
+    <col min="3" max="3" width="100.44140625" style="64" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="63" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="62" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="64" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="63" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="63" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="62" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="63" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="63" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="63" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="63" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="62" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="64" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="64" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="64" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="63" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="65"/>
+    <col min="21" max="21" width="67.77734375" style="64" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="63" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="63" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="63" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="63" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="63" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="63"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="64"/>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
+      <c r="A1" s="71"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="69"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="U2" s="70"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="U2" s="67"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="68" t="s">
         <v>463</v>
       </c>
-      <c r="P3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="67"/>
+      <c r="P3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="64"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="69" t="s">
         <v>492</v>
       </c>
-      <c r="P4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="67"/>
+      <c r="P4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="64"/>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="70" t="s">
         <v>494</v>
       </c>
       <c r="D5" s="2"/>
@@ -12232,7 +12849,7 @@
       <c r="B6" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="70" t="s">
         <v>496</v>
       </c>
       <c r="D6" s="2"/>
@@ -12242,7 +12859,7 @@
       <c r="B7" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="70" t="s">
         <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -12250,11 +12867,11 @@
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="69" t="s">
         <v>499</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="73"/>
+      <c r="C8" s="70"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:22">
@@ -12264,7 +12881,7 @@
       <c r="B9" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="70" t="s">
         <v>502</v>
       </c>
       <c r="D9" s="2"/>
@@ -12276,7 +12893,7 @@
       <c r="B10" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="70" t="s">
         <v>504</v>
       </c>
       <c r="D10" s="2"/>
@@ -12288,7 +12905,7 @@
       <c r="B11" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="70" t="s">
         <v>506</v>
       </c>
       <c r="D11" s="2"/>
@@ -12300,7 +12917,7 @@
       <c r="B12" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="70" t="s">
         <v>507</v>
       </c>
       <c r="D12" s="1"/>
@@ -12312,7 +12929,7 @@
       <c r="B13" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="70" t="s">
         <v>509</v>
       </c>
       <c r="D13" s="1"/>
@@ -12324,7 +12941,7 @@
       <c r="B14" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="64" t="s">
         <v>510</v>
       </c>
     </row>
@@ -12375,10 +12992,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="62"/>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -12534,10 +13151,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="62"/>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -12617,10 +13234,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="62"/>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -12760,10 +13377,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="62"/>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -12908,12 +13525,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -13025,10 +13642,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="62"/>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>

--- a/4 четверть_9_JavaScript_Vue.xlsx
+++ b/4 четверть_9_JavaScript_Vue.xlsx
@@ -8,19 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0D4ED4-F60B-426D-BFC4-11E4C350C1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A097F00-2AE3-4C7F-B2B7-67E7DEFC1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Название 1-3" sheetId="12" r:id="rId1"/>
-    <sheet name="Vue Css" sheetId="21" r:id="rId2"/>
-    <sheet name="URL to login after REMOTE auth" sheetId="20" r:id="rId3"/>
-    <sheet name="ElComponent" sheetId="18" r:id="rId4"/>
-    <sheet name="El-dialog" sheetId="19" r:id="rId5"/>
-    <sheet name="Vuetify" sheetId="15" r:id="rId6"/>
-    <sheet name="snippets Vue" sheetId="14" r:id="rId7"/>
-    <sheet name="download CSV" sheetId="16" r:id="rId8"/>
+    <sheet name="URL to login after REMOTE auth" sheetId="20" r:id="rId2"/>
+    <sheet name="Vuetify" sheetId="15" r:id="rId3"/>
+    <sheet name="snippets Vue" sheetId="14" r:id="rId4"/>
+    <sheet name="download CSV" sheetId="16" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="478">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -7115,396 +7112,6 @@
       </rPr>
       <t xml:space="preserve">Компонент &lt;Transition&gt; </t>
     </r>
-  </si>
-  <si>
-    <t>Vue Css</t>
-  </si>
-  <si>
-    <t>`https://element.eleme.io/#/en-US/component/date-picker</t>
-  </si>
-  <si>
-    <t>ElComponent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        &lt;div class="response_block" v-if="statusObject.responseBlock"&gt;
-            &lt;div v-if="tfaAccessChannel === 'TOTP'"&gt;
-                &lt;div class="confirm_totp_input_block text-center"&gt;
-                  &lt;i
-                    :class="responseMsg.status
-                      ? 'el-icon-success'
-                      : 'el-icon-error'"
-                    :style="{
-                      fontSize: '60px',
-                      color: responseMsg.status ? '#67C23A' : '#F56C6C'
-                    }"
-                  &gt;&lt;/i&gt;
-                  &lt;h2&gt;
-                    {{ responseMsg.status ? 'Аутентификатор подключен' : 'Ошибка' }}
-                  &lt;/h2&gt;
-                  &lt;p v-if="responseMsg.message != null"&gt;{{ responseMsg.message }}&lt;/p&gt;
-                &lt;/div&gt;
-                &lt;div slot="footer" class="select_block"&gt;
-                  &lt;el-button type="primary" @click="handleClose"&gt;
-                    Закрыть
-                  &lt;/el-button&gt;
-                &lt;/div&gt;
-            &lt;/div&gt;
-        &lt;/div&gt;
-    &lt;/el-dialog&gt;
-&lt;/div&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        &lt;div class="otp_input_block" v-if="statusObject.newTotpInputBlock"&gt;
-            &lt;div v-if="tfaAccessChannel === 'TOTP'"&gt;
-                &lt;div class='input_block'&gt;
-                    &lt;otpInputScreen
-                        :tfaUserOtp="tfaUserOtp"
-                        :successSendOtpMessage="successSendOtp.message"
-                        :errorOtpMessage="errorOtpMessage"
-                        @nullifyErrorOtpMessage="nullifyErrorOtpMessage"
-                        @enterEvent="validateSecondFactorForNewSecretSetup()"
-                        @changeTfaUserOtp="changeTfaUserOtp"
-                    &gt;
-                    &lt;/otpInputScreen&gt;
-                &lt;/div&gt;
-                &lt;div class="select_block"&gt;
-                    &lt;span slot="footer" class="dialog-footer"&gt;
-                        &lt;el-button @click="statusSwitcher('afterOtpBlock')"&gt;Назад&lt;/el-button&gt;
-                        &lt;el-button type="primary" @click="validateSecondFactorForNewSecretSetup()"&gt;Отправить&lt;/el-button&gt;
-                    &lt;/span&gt;
-                &lt;/div&gt;
-            &lt;/div&gt;
-        &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>&lt;div&gt;
-    &lt;el-dialog
-        :title="tfaAccessChannel !== 'TelegramChat' ? `Подключение ${title}`: null"
-        class="totp_setting_dialog"
-        :visible.sync="dialogVisible"
-        width="35%"
-        :before-close="handleClose"
-        v-loading="loading"
-        &gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        &lt;div class="before_otp_block" v-if="statusObject.beforeOtpBlock"&gt;
-            &lt;div class='input_block'&gt;
-                &lt;span v-if="tfaAccessChannel === 'TelegramChat'"&gt;Хотите изменить номер телефона?&lt;/span&gt;
-                &lt;span v-if="tfaAccessChannel === 'TOTP'"&gt;Хотите изменить приложение-аутентификатор?&lt;/span&gt;
-            &lt;/div&gt;
-            &lt;div class="select_block"&gt;
-                &lt;span slot="footer" class="dialog-footer"&gt;
-                    &lt;el-button @click="handleClose"&gt;Нет&lt;/el-button&gt;
-                    &lt;el-button type="primary" @click="{statusSwitcher('inOtpBlock'); tfaSendOtpForUser(tfaAccessChannel)}"&gt;Да&lt;/el-button&gt;
-                &lt;/span&gt;
-            &lt;/div&gt;
-        &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>statusObject.beforeOtpBlock</t>
-  </si>
-  <si>
-    <t>statusObject.inOtpBlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        &lt;div class="in_otp_block" v-if="statusObject.inOtpBlock"&gt;
-            &lt;div class="input_block"&gt;
-                &lt;otpInputScreen
-                    :tfaUserOtp="tfaUserOtp"
-                    :currentTimeLeft="currentTimeLeft"
-                    :timer="timer"
-                    :successSendOtpMessage="successSendOtp.message"
-                    :errorOtpMessage="errorOtpMessage"
-                    @nullifyErrorOtpMessage="nullifyErrorOtpMessage"
-                    @enterEvent="validateSecondFactor()"
-                    @changeTfaUserOtp="changeTfaUserOtp"
-                &gt;
-                &lt;/otpInputScreen&gt;
-            &lt;/div&gt;
-            &lt;div class="select_block"&gt;
-                &lt;span slot="footer" class="dialog-footer"&gt;
-                    &lt;el-button @click="handleClose"&gt;Отмена&lt;/el-button&gt;
-                    &lt;el-button type="primary" @click="validateSecondFactor()"&gt;Отправить&lt;/el-button&gt;
-                &lt;/span&gt;
-            &lt;/div&gt;
-        &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        &lt;div class="after_otp_block" v-if="statusObject.afterOtpBlock"&gt;
-            &lt;div v-if="tfaAccessChannel === 'TelegramChat'"&gt;
-                &lt;div&gt;
-                  &lt;p&gt;Корректировка данных телефона разрешена.&lt;/p&gt;                                     
-                &lt;/div&gt;
-            &lt;/div&gt;            
-            &lt;div v-if="tfaAccessChannel === 'TOTP'"&gt;
-                &lt;div class='confirm_totp_input_block'&gt;
-                    &lt;qr-code :size="200"
-                     color="#182649"
-                     :text="otpAuthUrl"&gt;&lt;/qr-code&gt;
-                    &lt;div class="text-center"&gt;Отсканируйте QR-код в приложении-аутентификаторе для синхронизации с вашей учетной записью.&lt;/div&gt;
-                    &lt;div class="text-center"&gt;После успешной синхронизации нажмите "Далее".&lt;/div&gt;
-                &lt;/div&gt;
-                &lt;div class="confirm_totp_select_block"&gt;
-                    &lt;span slot="footer" class="dialog-footer"&gt;
-                        &lt;el-button @click="handleClose"&gt;Закрыть&lt;/el-button&gt;
-                        &lt;el-button type="primary" @click="statusSwitcher('newTotpInputBlock')"&gt;Далее&lt;/el-button&gt;
-                    &lt;/span&gt;
-                &lt;/div&gt;
-            &lt;/div&gt;
-        &lt;/div&gt;</t>
-  </si>
-  <si>
-    <t>statusObject.afterOtpBlock</t>
-  </si>
-  <si>
-    <t>statusObject.responseBlock</t>
-  </si>
-  <si>
-    <t>statusObject.newTotpInputBlock</t>
-  </si>
-  <si>
-    <t>import Vue from 'vue';
-import template from './OtpInputDialog.html';
-import VueQRCodeComponent from 'vue-qrcode-component';
-import otpInputScreen from 'src/components/Login/OtpInputScreen/OtpInputScreen.js'
-import { mapState } from 'vuex';
-Vue.component('qr-code', VueQRCodeComponent);
-const speakeasy = require('speakeasy');
-export default Vue.extend({
-    template,
-    components: {
-      otpInputScreen,
-    },
-    name: 'otpInputDialog',
-    props: {
-        title: {
-            type: String,
-            default: () =&gt; 'Заголовок',
-        },
-        tfaAccessChannel: {
-            type: String,
-            default: () =&gt; '',
-        },
-        IdUser: {
-            type: String,
-            default: () =&gt; '',
-        },
-        dialogVisible: {
-            type: Boolean,
-            default: () =&gt; false,
-        },
-    },
-    mounted() {
-    },
-    data() {
-        return {
-            loading: false,
-            tfaSystemOtpHash: null,
-            tfaUserOtp: ['','','','','',''],
-            ttl: null,
-            currentTimeLeft: 59,
-            timer: 59,
-            ttlIntervalId: null,
-            otpAuthUrl: null,
-            errorOtpMessage: null,
-            statusObject: {
-                beforeOtpBlock : true,
-                inOtpBlock : false,
-                afterOtpBlock : false,
-                newTotpInputBlock: false,
-                responseBlock: false,
-            },
-            successSendOtp : { message: null },
-            newSecretFirstTime : null,
-            responseMsg: { message: null , status: null},
-        }
-    },
-    computed: {
-        ...mapState({
-            userData: state =&gt; state.user.userData,
-        }),
-        dialogVisibleComponent: {
-            get: function () {
-                let res = true;
-                if (this.dialogVisible) res = this.dialogVisible;
-                return res;
-            },
-            set: function (val) {
-                if(val === false) {
-                    this.statusSwitcher('beforeOtpBlock');
-                }  
-                this.$emit("changeDialogVisible", val);
-            },
-        },
-    },
-    methods: {
-        tfaSendOtpForUser(tfaAccessChannel){
-            this.tfaAccessChannel = tfaAccessChannel;
-            this.tfaUserOtp = ['','','','','',''];
-            if(this.tfaAccessChannel === 'TOTP') {
-                this.successSendOtp.message = 'Введите 6-значный код, указанный в приложении-аутентификаторе.';
-            } else {
-                this.loading = true;
-        	    this.$http.post('/api/auth/tfaSendOtpForUser', {
-        	    	tfaSelectedUserAccessChannel: this.tfaAccessChannel, 
-        	    	tfaUserData: this.userData,
-        	    }).then(response =&gt; {
-                    switch (response.data.otpSuccessfullySentMsg) {
-                        case 'otpSentToMail':
-                            this.successSendOtp.message = 'Введите 6-значный код, отправленный на Вашу электронную почту.'
-                            break;
-                        case 'otpSentToTelegram':
-                            this.successSendOtp.message = 'Введите 6-значный код, отправленный в Телеграм.'
-                            break;
-                        default:
-                            break;
-                    }
-                    this.tfaSystemOtpHash = response.data.tfaSystemOtpHash;
-                    this.ttl = (Date.now()/1000).floor() + this.timer;
-                    this.ttlIntervalId = setInterval(()=&gt;{
-                        this.currentTimeLeft = this.ttl - (Date.now()/1000).floor(1);
-                        if(this.currentTimeLeft &lt; 0) {
-                            clearInterval(this.ttlIntervalId);
-                            this.currentTimeLeft = this.timer;
-                            this.errorOtpMessage = 'В отведённый временной интервал не был получен 6-значный код.'
-                            setTimeout(()=&gt;{
-                                this.handleClose();
-                            }, 2000)
-                        }
-                    }, 100);
-                })
-                .catch(err =&gt; {
-                    let message = 'Сервис недоступен.';
-                    // switch (err.status) {
-                    //   case 503:
-                    //     message = 'Сбой двухфакторной авторизации.';
-                    //     break;
-                    //   default:
-                    //     message = this.$t('loginError');
-                    //     break;
-                    // }
-                    this.errorOtpMessage = message;
-                });
-            }
-            this.loading = false;
-        },
-        validateSecondFactor() {
-            if(this.currentTimeLeft &gt;= 0) {
-                this.loading = true;
-                this.$http.post('/api/auth/validateSecondFactor', {
-                    tfaSelectedUserAccessChannel: this.tfaAccessChannel,
-                    tfaUserOtp: this.tfaUserOtp.join(""), 
-                    tfaSystemOtpHash: this.tfaSystemOtpHash,
-                    tfaUserId: this.userData.IdUser,
-                })
-                .then(response =&gt; {
-                    this.loading = false;
-                    switch (this.tfaAccessChannel) {
-                        case 'TelegramChat':
-                            this.$emit('changeAccessToChangePhoneGranted', true);
-                            break;
-                        case 'TOTP':
-                            this.newSecretFirstTime = speakeasy.generateSecret({name: "Headway LK"});
-                            this.otpAuthUrl = this.newSecretFirstTime.otpauth_url;
-                            this.tfaUserOtp = ['','','','','',''];
-                            this.successSendOtp.message = 'Введите 6-значный код, указанный в приложении-аутентификаторе.';
-                            break;
-                        default:
-                            break;
-                    }
-                    this.statusSwitcher('afterOtpBlock');
-                })
-                .catch(err =&gt; {
-                    this.loading = false;
-                    let message = 'Сервис недоступен.';
-                    switch (err.status) { 
-                        case 503:
-                            message = 'Сбой двухфакторной аутентификации.';
-                            break;
-                        default:
-                            message = 'Введён недействительный 6-значный код. Попробуйте ещё раз.'
-                            break;
-                    }
-                    this.tfaUserOtp = ['','','','','',''];
-                    this.errorOtpMessage = message;
-                })
-            } 
-        },
-        validateSecondFactorForNewSecretSetup() {
-            let tfaSuccessfullyVerified = speakeasy.totp.verify({ 
-                secret: this.newSecretFirstTime.ascii, //'L7,ucxq, r&amp;RdN9LBh2IT5k4PCSZOFZAo', 
-                encoding: 'ascii', 
-                token: this.tfaUserOtp.join(""), //'102511'
-            });
-            if (tfaSuccessfullyVerified){
-              this.loading = true;
-              this.$http.post('/api/user/updateTotpSecret',{ 
-                IdUser: this.IdUser,
-                secret: this.newSecretFirstTime,
-              })
-                .then((response) =&gt; {
-                  this.loading = false;
-                  this.responseMsg.message = 'Синхронизация с вашим приложением успешно установлена.';
-                  this.responseMsg.status = true;
-                })
-                .catch((err) =&gt; {
-                  this.loading = false;
-                  this.responseMsg.message = 'К сожалению, в данный момент установка нового секретного ключа недоступна.';
-                  this.responseMsg.status = false;
-                })
-                .finally(()=&gt;this.statusSwitcher('responseBlock'))
-            } else {
-                this.tfaUserOtp = ['','','','','',''];
-                this.errorOtpMessage = 'Введён недействительный 6-значный код. Попробуйте ещё раз.';
-            }
-        },
-        changeTfaUserOtp(val) {
-            this.tfaUserOtp = val;
-        },
-        nullifyErrorOtpMessage() {
-            this.errorOtpMessage = null;
-        },
-        statusSwitcher(statusSelected){
-            this.statusObject = Object.map(this.statusObject, function(value, key) {
-                return key === statusSelected ? true : false
-            })
-        },
-        handleClose() {
-            clearInterval(this.ttlIntervalId);
-            this.tfaUserOtp = ['','','','','',''];
-            this.currentTimeLeft = this.timer;
-            this.errorOtpMessage = null;
-            this.dialogVisibleComponent = false;
-        },
-    },
-    watch: {
-    }
-});</t>
-  </si>
-  <si>
-    <t>Переключение между окнами диалога
-            statusObject: {
-                beforeOtpBlock : true,
-                inOtpBlock : false,
-                afterOtpBlock : false,
-                newTotpInputBlock: false,
-                responseBlock: false,
-            },
-        statusSwitcher(statusSelected){
-            this.statusObject = Object.map(this.statusObject, function(value, key) {
-                return key === statusSelected ? true : false
-            })
-        },</t>
-  </si>
-  <si>
-    <t>JS</t>
-  </si>
-  <si>
-    <t>html</t>
-  </si>
-  <si>
-    <t>El-dialog</t>
   </si>
   <si>
     <t>Вход в SPA после авторизации на стороннем сайте</t>
@@ -7645,380 +7252,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">data() {
-        return {
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">            activeStyleColor: {
-                backgroundColor: "#409EFF",
-                borderColor: "#409EFF",
-                color: "#fff",
-            },
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">        };
-    },</t>
-    </r>
-  </si>
-  <si>
-    <t>inline стили</t>
-  </si>
-  <si>
-    <t>несколько стилей</t>
-  </si>
-  <si>
-    <r>
-      <t>&lt;el-button</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> :style="{backgroundColor: "#409EFF", ...}"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  &gt; &lt;/el-button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>несколько стилей с условиями</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;el-button </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:style="{backgroundColor: item.length === 0 ? "#409EFF" : "#FFF", ...}"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&gt; &lt;/el-button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>несколько стилей, комбинированных в объект</t>
-  </si>
-  <si>
-    <r>
-      <t>&lt;el-button</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> :style="condformattingobj.colorformatting?.active ? activeStyleColor : {}"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &gt; &lt;/el-button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>классы</t>
-  </si>
-  <si>
-    <t>Подход 1</t>
-  </si>
-  <si>
-    <t>один class</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting ? 'btn-danger' : null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>Подход 2</t>
-  </si>
-  <si>
-    <r>
-      <t>&lt;button  v-bind:class="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{'btn-danger': !colorEdit || !baseSettings.editUserCurrentSetting}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>несколько class</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        [
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">colorEdit &amp;&amp; baseSettings.editUserCurrentSetting ? 'btn-danger' : null ,
-          colorEdit &amp;&amp; baseSettings.editUserCurrentSetting ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        {
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'btn-danger': colorEdit &amp;&amp; baseSettings.editUserCurrentSetting,
-          'btn-default': !colorEdit || !baseSettings.editUserCurrentSetting, 
-          'btn-primary': colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         }
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <t>Микс подход</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-        v-bind:class="[
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'custom_class_1',
-            {'btn-danger': !colorEdit || !baseSettings.editUserCurrentSetting}, 
-           colorEdit &amp;&amp; baseSettings.editUserCurrentSetting ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]"
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>&lt;template&gt;
-  &lt;button :class="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>buttonClass</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">"&gt;Кнопка&lt;/button&gt;
-&lt;/template&gt;
-&lt;script&gt;
-export default {
-  computed: {
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">    buttonClass() {
-      return this.checkBtn(this.table.TableNameReal) 
-        ? 'btn-primary' 
-        : 'hwc-btn-unactive';
-    }
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  }
-}
-&lt;/script&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">    &lt;div class="gr-bd_content_receiveraddmenu" &gt;
 </t>
     </r>
@@ -8602,6 +7835,20 @@
  transform: translateX(-100%); //появление слева-направо
 }</t>
     </r>
+  </si>
+  <si>
+    <t>directives: {
+    focus: {
+        bind(el)      {},  // директиву связали с элементом (еще в виртуальном DOM)
+        inserted(el)  {},  // элемент вставлен в реальный DOM ⬅️ ТЫ ЗДЕСЬ
+        update(el)    {},  // обновился компонент, но дочерние еще не обновились
+        componentUpdated(el) {}, // обновился компонент и все дочерние
+        unbind(el)    {}   // директиву отвязали от элемента
+    }
+}</t>
+  </si>
+  <si>
+    <t>Кастомные директивы</t>
   </si>
 </sst>
 </file>
@@ -9045,9 +8292,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -9198,63 +8445,26 @@
     <xf numFmtId="49" fontId="5" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="13" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="13" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -10343,7 +9553,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V285"/>
+  <dimension ref="A2:V287"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -10720,7 +9930,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="43.2">
+    <row r="38" spans="1:4" ht="57.6">
       <c r="B38" s="17" t="s">
         <v>190</v>
       </c>
@@ -12669,17 +11879,17 @@
       <c r="C275" s="44"/>
     </row>
     <row r="276" spans="1:4" ht="409.6">
-      <c r="A276" s="74" t="s">
-        <v>512</v>
+      <c r="A276" s="58" t="s">
+        <v>473</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C276" s="74" t="s">
-        <v>513</v>
-      </c>
-      <c r="D276" s="74" t="s">
-        <v>514</v>
+        <v>472</v>
+      </c>
+      <c r="C276" s="58" t="s">
+        <v>474</v>
+      </c>
+      <c r="D276" s="58" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -12746,6 +11956,16 @@
     <row r="285" spans="1:4" ht="216">
       <c r="C285" s="46" t="s">
         <v>441</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="144">
+      <c r="C287" s="61" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -12757,204 +11977,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F60E-4ADA-4D72-A128-02A784820C6B}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="36" style="63" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="64" customWidth="1"/>
-    <col min="3" max="3" width="100.44140625" style="64" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="63" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="62" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="63" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="64" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="63" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="63" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="62" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="63" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="63" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="63" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="63" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="62" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="64" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="64" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="64" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="63" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="65"/>
-    <col min="21" max="21" width="67.77734375" style="64" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="63" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="63" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="63" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="63" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="63" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="63"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="71"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="U2" s="67"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="C3" s="68" t="s">
-        <v>463</v>
-      </c>
-      <c r="P3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="64"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="69" t="s">
-        <v>492</v>
-      </c>
-      <c r="P4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C5" s="70" t="s">
-        <v>494</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>496</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" ht="129.6">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>498</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="69" t="s">
-        <v>499</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="70"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>502</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C10" s="70" t="s">
-        <v>504</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" ht="115.2">
-      <c r="A11" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>506</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:22" ht="129.6">
-      <c r="A12" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C12" s="70" t="s">
-        <v>507</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:22" ht="100.8">
-      <c r="A13" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>509</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:22" ht="216">
-      <c r="A14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>510</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D825E87-AA95-4E22-841B-0301C795364F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -12992,10 +12014,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="72"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -13017,19 +12039,19 @@
       <c r="U2" s="23"/>
     </row>
     <row r="3" spans="1:22">
-      <c r="C3" s="55" t="s">
-        <v>482</v>
+      <c r="C3" s="51" t="s">
+        <v>463</v>
       </c>
       <c r="P3" s="19"/>
       <c r="U3" s="19"/>
       <c r="V3" s="20"/>
     </row>
     <row r="4" spans="1:22" s="18" customFormat="1">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="52" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="20"/>
-      <c r="C4" s="61"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="19"/>
       <c r="F4" s="19"/>
       <c r="G4" s="20"/>
@@ -13048,12 +12070,12 @@
       <c r="V4" s="19"/>
     </row>
     <row r="5" spans="1:22" s="18" customFormat="1">
-      <c r="A5" s="60" t="s">
-        <v>490</v>
+      <c r="A5" s="56" t="s">
+        <v>471</v>
       </c>
       <c r="B5" s="20"/>
-      <c r="C5" s="61" t="s">
-        <v>489</v>
+      <c r="C5" s="57" t="s">
+        <v>470</v>
       </c>
       <c r="D5" s="19"/>
       <c r="F5" s="19"/>
@@ -13074,30 +12096,30 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="57" t="s">
-        <v>486</v>
+      <c r="C6" s="53" t="s">
+        <v>467</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:22" ht="230.4">
       <c r="A7" s="1" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="57" t="s">
-        <v>483</v>
+      <c r="C7" s="53" t="s">
+        <v>464</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:22" ht="409.6">
-      <c r="A8" s="58" t="s">
-        <v>487</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>488</v>
+      <c r="A8" s="54" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -13112,234 +12134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10679322-B66C-4A2A-BA00-35BB5CDCF52D}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="36" style="19" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="20" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="19" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="19" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="18" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="19" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="19" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="19" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="18" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="20" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="20" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="20" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="19" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="21"/>
-    <col min="21" max="21" width="67.77734375" style="20" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="19" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="19" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="19" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="19" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="19" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="72"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="U2" s="23"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="C3" s="51" t="s">
-        <v>465</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>464</v>
-      </c>
-      <c r="P3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB89C57B-4415-4E7B-A67D-1BB77B7555B3}">
-  <sheetPr>
-    <tabColor theme="4" tint="0.39997558519241921"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V12"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="36" style="19" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="20" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="19" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="19" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="18" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="19" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="19" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="19" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="18" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="20" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="20" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="20" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="19" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="21"/>
-    <col min="21" max="21" width="67.77734375" style="20" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="19" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="19" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="19" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="19" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="19" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22">
-      <c r="A1" s="72"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="U2" s="23"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="C3" s="51" t="s">
-        <v>481</v>
-      </c>
-      <c r="D3" s="52"/>
-      <c r="P3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="20"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="54" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="129.6">
-      <c r="C5" s="53" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="216">
-      <c r="A6" s="52" t="s">
-        <v>470</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="316.8">
-      <c r="A7" s="52" t="s">
-        <v>471</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="360">
-      <c r="A8" s="52" t="s">
-        <v>474</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="331.2">
-      <c r="A9" s="52" t="s">
-        <v>476</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="374.4">
-      <c r="A10" s="52" t="s">
-        <v>475</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="54" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="409.6">
-      <c r="B12" s="53" t="s">
-        <v>478</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>477</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECA43F35-896E-4AF4-9490-A6E7A4167F76}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13377,10 +12172,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="72"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -13487,7 +12282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28329730-A06B-4EF9-BB9C-FF8DE4151289}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13525,12 +12320,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
@@ -13604,7 +12399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5F33576-E5EF-47DE-AAF9-4DE2FAE178AB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -13642,10 +12437,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="72"/>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="22"/>
